--- a/TestData/checkout_success.xlsx
+++ b/TestData/checkout_success.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software Testing\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software Testing\TestSauceDemo\WebSauceDemo\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD80115-A85A-4B0E-BF5A-1CF66C45D806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2AC37E-A70D-47E6-A8FB-68A051CA78A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{74336404-81A4-4376-ACDE-BCD246E9141B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Nguyen</t>
   </si>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B5DDCDA-BFFB-4145-9C7A-3CC479EB5F59}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -538,16 +538,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>220000</v>
+        <v>110000</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -555,16 +555,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>110000</v>
+        <v>830000</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -572,35 +572,18 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>830000</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>830000</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
         <v>14</v>
       </c>
     </row>
